--- a/MU/Test upload format/Normal/2025 - 2026/Cp4 25-26.xlsx
+++ b/MU/Test upload format/Normal/2025 - 2026/Cp4 25-26.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="55">
   <si>
     <t>custid</t>
   </si>
@@ -74,22 +74,124 @@
     <t>pan</t>
   </si>
   <si>
-    <t>MUSML006</t>
+    <t>taruncategoryearlier</t>
+  </si>
+  <si>
+    <t>accountsrepaidsatisfactorily</t>
+  </si>
+  <si>
+    <t>AnyLoansInNPASuitFiledSettledOTS</t>
+  </si>
+  <si>
+    <t>modifiedloancat</t>
+  </si>
+  <si>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>CR13Q1252614</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>01-04-2025</t>
+  </si>
+  <si>
+    <t>100001</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>CR13Q1252615</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>CR13Q1252616</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>CR13Q1252617</t>
+  </si>
+  <si>
+    <t>300000</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>01-01-2031</t>
-  </si>
-  <si>
-    <t>01-09-2026</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>MUSML007</t>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>CR13Q1252601</t>
+  </si>
+  <si>
+    <t>01-04-2029</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>CR13Q1252602</t>
+  </si>
+  <si>
+    <t>Q2CR1301</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>01-07-2025</t>
+  </si>
+  <si>
+    <t>Q2CR1302</t>
+  </si>
+  <si>
+    <t>Q2CR1303</t>
+  </si>
+  <si>
+    <t>Q2CR1304</t>
+  </si>
+  <si>
+    <t>Q2CR1305</t>
+  </si>
+  <si>
+    <t>Q2CR1306</t>
+  </si>
+  <si>
+    <t>Q2CR1307</t>
+  </si>
+  <si>
+    <t>Q2CR1308</t>
+  </si>
+  <si>
+    <t>Q2CR1309</t>
+  </si>
+  <si>
+    <t>Q2CR1310</t>
+  </si>
+  <si>
+    <t>Q2CR1311</t>
+  </si>
+  <si>
+    <t>Q2CR1312</t>
   </si>
 </sst>
 </file>
@@ -102,7 +204,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +219,18 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -263,12 +377,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -467,16 +599,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,154 +730,184 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,12 +916,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1279,141 +1441,921 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="16.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="12.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="16.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13.4285714285714" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="13" max="13" width="13.4285714285714" customWidth="1"/>
     <col min="14" max="14" width="17.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:20">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1">
-        <v>50000</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1</v>
-      </c>
-      <c r="M2" s="7">
-        <v>100000</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>17</v>
+    <row r="2" s="2" customFormat="1" ht="25.5" spans="1:20">
+      <c r="A2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="12">
+        <v>1</v>
+      </c>
+      <c r="L2" s="12">
+        <v>1</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:14">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1">
-        <v>50000</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="M3" s="7">
-        <v>100000</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>17</v>
+    <row r="3" s="2" customFormat="1" ht="25.5" spans="1:20">
+      <c r="A3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="12">
+        <v>1</v>
+      </c>
+      <c r="L3" s="12">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="25.5" spans="1:20">
+      <c r="A4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="12">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="25.5" spans="1:20">
+      <c r="A5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="10">
+        <v>10000</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="12">
+        <v>1</v>
+      </c>
+      <c r="L5" s="12">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="25.5" spans="1:20">
+      <c r="A6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="17">
+        <v>1</v>
+      </c>
+      <c r="K6" s="17">
+        <v>1</v>
+      </c>
+      <c r="L6" s="17">
+        <v>1</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:20">
+      <c r="A7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="17">
+        <v>1</v>
+      </c>
+      <c r="K7" s="17">
+        <v>1</v>
+      </c>
+      <c r="L7" s="17">
+        <v>1</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" spans="1:20">
+      <c r="A8" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" spans="1:20">
+      <c r="A9" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="1:20">
+      <c r="A10" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="1:20">
+      <c r="A11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4">
+        <v>1</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" spans="1:20">
+      <c r="A12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="1:20">
+      <c r="A13" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4">
+        <v>1</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:20">
+      <c r="A14" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" spans="1:20">
+      <c r="A15" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4">
+        <v>1</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" spans="1:20">
+      <c r="A16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1</v>
+      </c>
+      <c r="K16" s="4">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>1</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" spans="1:20">
+      <c r="A17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" spans="1:20">
+      <c r="A18" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" spans="1:20">
+      <c r="A19" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
